--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_115_R12.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_115_R12.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5958</v>
+        <v>6.025</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3946</v>
+        <v>7.059</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7988</v>
+        <v>-1.034</v>
       </c>
       <c r="G2" t="n">
         <v>0.1859</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2087</v>
+        <v>0.6379</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5149</v>
+        <v>0.1496</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7235</v>
+        <v>0.4883</v>
       </c>
       <c r="V2" t="n">
         <v>5.8971</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9405</v>
+        <v>4.7606</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9102</v>
+        <v>5.112</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0303</v>
+        <v>-0.3515</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.0509</v>
+        <v>-0.9176</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2413</v>
+        <v>1.3609</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8096</v>
+        <v>-2.2785</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0473</v>
+        <v>2.0204</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0105</v>
+        <v>2.77</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0368</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0982</v>
+        <v>-2.9381</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2518</v>
+        <v>-1.4091</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8464</v>
+        <v>-1.529</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9735</v>
+        <v>0.7863</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9505</v>
+        <v>-0.1766</v>
       </c>
       <c r="U3" t="n">
-        <v>2.023</v>
+        <v>0.963</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3943</v>
+        <v>3.5002</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1444</v>
+        <v>3.5002</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6079</v>
+        <v>1.6074</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0937</v>
+        <v>2.2156</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4859</v>
+        <v>-0.6082</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9176</v>
+        <v>-2.0509</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3609</v>
+        <v>-1.2413</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.2785</v>
+        <v>-0.8096</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0204</v>
+        <v>0.0473</v>
       </c>
       <c r="K4" t="n">
-        <v>2.77</v>
+        <v>0.0105</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9381</v>
+        <v>-2.0982</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4091</v>
+        <v>-1.2518</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.529</v>
+        <v>-0.8464</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3664</v>
+        <v>1.6403</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1949</v>
+        <v>0.2559</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8285</v>
+        <v>1.3845</v>
       </c>
       <c r="V4" t="n">
-        <v>3.5002</v>
+        <v>0.3943</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5002</v>
+        <v>2.1444</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9854000000000001</v>
+        <v>1.1273</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5076</v>
+        <v>1.5823</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5223</v>
+        <v>-0.455</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7093</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6071</v>
+        <v>0.749</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6449</v>
+        <v>0.7196</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0378</v>
+        <v>0.0294</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5361</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6303</v>
+        <v>-0.2729</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8481</v>
+        <v>1.7433</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2178</v>
+        <v>-2.0162</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0876</v>
@@ -922,13 +922,13 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5736</v>
+        <v>0.6704</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0148</v>
+        <v>-0.0901</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5588</v>
+        <v>0.7604</v>
       </c>
       <c r="V6" t="n">
         <v>1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7431</v>
+        <v>-0.5169</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0004</v>
+        <v>0.1931</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7436</v>
+        <v>-0.7099</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8585</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0444</v>
+        <v>0.1819</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0668</v>
+        <v>0.1259</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9392</v>
+        <v>-1.04</v>
       </c>
       <c r="E8" t="n">
         <v>0.7027</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6419</v>
+        <v>-1.7427</v>
       </c>
       <c r="G8" t="n">
         <v>2.3784</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.083</v>
+        <v>-0.1838</v>
       </c>
       <c r="T8" t="n">
         <v>-0.5975</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5144</v>
+        <v>0.4136</v>
       </c>
       <c r="V8" t="n">
         <v>-2.5387</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2729</v>
+        <v>-2.1307</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2695</v>
+        <v>-1.2793</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0033</v>
+        <v>-0.8515</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0172</v>
+        <v>-1.0919</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8428</v>
+        <v>-1.5102</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1744</v>
+        <v>0.4183</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6081</v>
+        <v>-0.9845</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6449</v>
+        <v>-0.9845</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0368</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4091</v>
+        <v>-0.1074</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1979</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2112</v>
+        <v>0.4183</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.6237</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6026</v>
+        <v>0.2653</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3566</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.246</v>
+        <v>0.3282</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5085</v>
+        <v>-2.7886</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5899</v>
+        <v>-1.6314</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9187</v>
+        <v>-1.1572</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0919</v>
+        <v>-3.3514</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5102</v>
+        <v>-0.8989</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4183</v>
+        <v>-2.4525</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9845</v>
+        <v>-0.0237</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9845</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.7127</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1074</v>
+        <v>-3.3277</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-1.5879</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4183</v>
+        <v>-1.7398</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1125</v>
+        <v>0.867</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3734</v>
+        <v>0.016</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2609</v>
+        <v>0.8509</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3953</v>
+        <v>-2.8551</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7676</v>
+        <v>-1.7846</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6277</v>
+        <v>-1.0705</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3514</v>
+        <v>-3.0172</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8989</v>
+        <v>-1.8428</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4525</v>
+        <v>-1.1744</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0237</v>
+        <v>-0.6081</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6889999999999999</v>
+        <v>-0.6449</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7127</v>
+        <v>0.0368</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3277</v>
+        <v>-2.4091</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5879</v>
+        <v>-1.1979</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7398</v>
+        <v>-1.2112</v>
       </c>
       <c r="P11" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.6237</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7398</v>
+        <v>1.0203</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1202</v>
+        <v>0.8415</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3804</v>
+        <v>0.1788</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5361</v>
+        <v>-0.3943</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7917</v>
+        <v>-4.0601</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.509</v>
+        <v>-3.8445</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2827</v>
+        <v>-0.2155</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6252</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0448</v>
+        <v>0.7765</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2908</v>
+        <v>0.3736</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3356</v>
+        <v>0.4028</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8197</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8907999999999987</v>
+        <v>-0.1440000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>9.321299999999999</v>
+        <v>10.0682</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.2124</v>
+        <v>-10.2122</v>
       </c>
       <c r="G13" t="n">
         <v>-13.1453</v>
@@ -1459,7 +1459,7 @@
         <v>-10.2879</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1598</v>
+        <v>1.159800000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.9173</v>
@@ -1468,22 +1468,22 @@
         <v>15.077</v>
       </c>
       <c r="S13" t="n">
-        <v>6.664200000000001</v>
+        <v>7.411099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8082999999999996</v>
+        <v>1.5551</v>
       </c>
       <c r="U13" t="n">
-        <v>5.855700000000001</v>
+        <v>5.8559</v>
       </c>
       <c r="V13" t="n">
-        <v>4.430600000000002</v>
+        <v>4.430599999999999</v>
       </c>
       <c r="W13" t="n">
         <v>13.0393</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.608700000000001</v>
+        <v>-8.608699999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.2524</v>
+        <v>9.3874</v>
       </c>
       <c r="E14" t="n">
-        <v>10.1173</v>
+        <v>10.3532</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8649</v>
+        <v>-0.9657</v>
       </c>
       <c r="G14" t="n">
         <v>11.3455</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7789</v>
+        <v>-0.6438</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0455</v>
+        <v>-0.8096</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2667</v>
+        <v>0.1658</v>
       </c>
       <c r="V14" t="n">
         <v>2.3969</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1072</v>
+        <v>1.7369</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8158</v>
+        <v>3.5799</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7086</v>
+        <v>-1.8431</v>
       </c>
       <c r="G15" t="n">
         <v>2.6946</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2627</v>
+        <v>-0.633</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4832</v>
+        <v>-0.7191</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2205</v>
+        <v>0.0861</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7886</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6585</v>
+        <v>1.0624</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5917</v>
+        <v>0.8276</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0668</v>
+        <v>0.2348</v>
       </c>
       <c r="G16" t="n">
         <v>-1.9071</v>
@@ -1702,13 +1702,13 @@
         <v>2.5515</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5942</v>
+        <v>-1.1903</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1949</v>
+        <v>-0.959</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3993</v>
+        <v>-0.2313</v>
       </c>
       <c r="V16" t="n">
         <v>1.6083</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1916</v>
+        <v>0.1416</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8498</v>
+        <v>-0.7319</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0415</v>
+        <v>0.8734</v>
       </c>
       <c r="G17" t="n">
         <v>1.4822</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0136</v>
+        <v>-0.0365</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6721</v>
+        <v>-0.5542</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6858</v>
+        <v>0.5177</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RUBSTAVICIUS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08550000000000001</v>
+        <v>0.0358</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1904</v>
+        <v>3.0511</v>
       </c>
       <c r="F18" t="n">
-        <v>0.105</v>
+        <v>-3.0153</v>
       </c>
       <c r="G18" t="n">
-        <v>0.012</v>
+        <v>2.9619</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1452</v>
+        <v>0.5295</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1573</v>
+        <v>2.4324</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0336</v>
+        <v>3.5739</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0336</v>
+        <v>1.6133</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.9606</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0216</v>
+        <v>-0.612</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1788</v>
+        <v>-1.0838</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1573</v>
+        <v>0.4718</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0975</v>
+        <v>-0.3332</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.224</v>
+        <v>-0.5228</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1265</v>
+        <v>0.1896</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-3.7527</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-3.7527</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>M. RUBSTAVICIUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1551</v>
+        <v>-0.2199</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0511</v>
+        <v>-0.1904</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2062</v>
+        <v>-0.0295</v>
       </c>
       <c r="G19" t="n">
-        <v>2.9619</v>
+        <v>0.012</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5295</v>
+        <v>-0.1452</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4324</v>
+        <v>0.1573</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5739</v>
+        <v>0.0336</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6133</v>
+        <v>0.0336</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9606</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.612</v>
+        <v>-0.0216</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0838</v>
+        <v>-0.1788</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4718</v>
+        <v>0.1573</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5241</v>
+        <v>-0.232</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5228</v>
+        <v>-0.224</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0013</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.7527</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.7527</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7647</v>
+        <v>-0.7083</v>
       </c>
       <c r="E20" t="n">
         <v>-0.0411</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7237</v>
+        <v>-0.6672</v>
       </c>
       <c r="G20" t="n">
         <v>0.1585</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1489</v>
+        <v>0.2054</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2236</v>
+        <v>0.2801</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.19</v>
+        <v>-1.6516</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.547</v>
+        <v>-2.3111</v>
       </c>
       <c r="F21" t="n">
-        <v>0.357</v>
+        <v>0.6595</v>
       </c>
       <c r="G21" t="n">
         <v>-2.279</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4651</v>
+        <v>-0.9267</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2696</v>
+        <v>-1.0337</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1955</v>
+        <v>0.107</v>
       </c>
       <c r="V21" t="n">
         <v>0.3943</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3468</v>
+        <v>-1.8699</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6444</v>
+        <v>-1.5264</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7024</v>
+        <v>-0.3434</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0709</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9744</v>
+        <v>-0.4975</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.601</v>
+        <v>-0.242</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7774</v>
+        <v>-2.974</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0023</v>
+        <v>-1.3561</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7751</v>
+        <v>-1.6178</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8575</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-1.1165</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0351</v>
+        <v>-0.389</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8847</v>
+        <v>-0.7275</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9994</v>
+        <v>-3.2632</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1608</v>
+        <v>-2.5146</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8386</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3951</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.21</v>
+        <v>-0.4738</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0395</v>
+        <v>-0.3143</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2495</v>
+        <v>-0.1595</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4665</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8908</v>
+        <v>1.6772</v>
       </c>
       <c r="E25" t="n">
-        <v>9.140099999999997</v>
+        <v>9.1402</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.2492</v>
+        <v>-7.4628</v>
       </c>
       <c r="G25" t="n">
         <v>13.1451</v>
@@ -2404,13 +2404,13 @@
         <v>13.9173</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.664300000000001</v>
+        <v>-5.877899999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.8558</v>
+        <v>-5.8559</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8082</v>
+        <v>-0.02190000000000006</v>
       </c>
       <c r="V25" t="n">
         <v>-4.4306</v>
